--- a/output/quickfixclose20_portfolio_daily.xlsx
+++ b/output/quickfixclose20_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5751,20 +5751,68 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
+        <v>288491.24</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>5529.07</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>282962.18</v>
+      </c>
+      <c r="E186" t="n">
+        <v>3</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>288491.24</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>5529.07</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>282962.18</v>
+      </c>
+      <c r="E187" t="n">
+        <v>3</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
         <v>288388.48</v>
       </c>
-      <c r="C186" s="5" t="n">
+      <c r="C188" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D186" s="5" t="n">
+      <c r="D188" s="5" t="n">
         <v>288388.48</v>
       </c>
-      <c r="E186" t="n">
+      <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
         <is>
           <t>Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>

--- a/output/quickfixclose20_portfolio_daily.xlsx
+++ b/output/quickfixclose20_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>288,388.48</t>
+          <t>309,239.77</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+188.39%</t>
+          <t>+209.24%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>296,940  (+196.94%)</t>
+          <t>318,438  (+218.44%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,060  (8.6 pts of return)</t>
+          <t>4,109  (9.2 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8.6x</t>
+          <t>9.6x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6.4 bars</t>
+          <t>6.6 bars</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+14.67R  (best +56.18R)</t>
+          <t>+14.51R  (best +56.18R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16,803  (+14.67%)</t>
+          <t>17,040  (+14.51%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5799,22 +5799,82 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>288388.48</v>
+        <v>288491.24</v>
       </c>
       <c r="C188" s="5" t="n">
+        <v>5529.07</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>282962.18</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>309324.3</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>12205.7</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>297118.6</v>
+      </c>
+      <c r="E189" t="n">
+        <v>5</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Corn_CBOT_Futures, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 2,830); Nasdaq_100_E_mini short (risk 2,801); S_P_500_E_mini short (risk 2,773)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures exit_close (+20,833)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>309239.77</v>
+      </c>
+      <c r="C190" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D188" s="5" t="n">
-        <v>288388.48</v>
-      </c>
-      <c r="E188" t="n">
+      <c r="D190" s="5" t="n">
+        <v>309239.77</v>
+      </c>
+      <c r="E190" t="n">
         <v>0</v>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,971)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9603,14 +9663,22 @@
           <t>2026-07-08</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>20</v>
+      </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>12.098</v>
       </c>
       <c r="G74" t="n">
-        <v>0.02</v>
+        <v>0.039</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.02</v>
+        <v>12.059</v>
       </c>
       <c r="I74" s="5" t="n">
         <v>186339.75</v>
@@ -9618,15 +9686,15 @@
       <c r="J74" s="5" t="n">
         <v>2590.12</v>
       </c>
-      <c r="K74" s="6" t="n">
-        <v>-50.79</v>
+      <c r="K74" s="7" t="n">
+        <v>31233.73</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>364459.08</v>
+        <v>395807.41</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9733,7 @@
         <v>-63.81</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>364509.87</v>
+        <v>395743.6</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -9708,9 +9776,181 @@
         <v>-42.25</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>364416.83</v>
+        <v>395673.96</v>
       </c>
       <c r="M76" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>356050.95</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>4949.11</v>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>-17.18</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>395717.23</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>351101.84</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>4880.32</v>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>395734.41</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>346221.52</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>4812.48</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>395716.21</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>375232.9</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>5215.74</v>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>-8.92</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>395734.68</v>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>

--- a/output/quickfixclose20_portfolio_daily.xlsx
+++ b/output/quickfixclose20_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>309,239.77</t>
+          <t>306,233.98</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+209.24%</t>
+          <t>+206.23%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>318,438  (+218.44%)</t>
+          <t>315,379  (+215.38%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,109  (9.2 pts of return)</t>
+          <t>4,144  (9.1 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9.6x</t>
+          <t>9.5x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6.6 bars</t>
+          <t>6.5 bars</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,435  (-1.28%)</t>
+          <t>-1,462  (-1.28%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5855,26 +5855,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>309239.77</v>
+        <v>309324.3</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>15176.89</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>294147.42</v>
+      </c>
+      <c r="E190" t="n">
+        <v>6</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Corn_CBOT_Futures, Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,971)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>306233.98</v>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D191" s="5" t="n">
+        <v>306233.98</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>309239.77</v>
-      </c>
-      <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 2,971)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 2,941); NY_Palladium_Futures short (risk 2,912)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX stop (-2,992); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9776,7 +9804,7 @@
         <v>-42.25</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>395673.96</v>
+        <v>390397.68</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9819,7 +9847,7 @@
         <v>-17.18</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>395717.23</v>
+        <v>390440.95</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -9862,7 +9890,7 @@
         <v>-0.27</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>395734.41</v>
+        <v>390491.93</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9905,7 +9933,7 @@
         <v>-1.02</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>395716.21</v>
+        <v>390439.94</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9929,14 +9957,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>375232.9</v>
@@ -9945,12 +9981,98 @@
         <v>5215.74</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>-8.92</v>
+        <v>-5251.4</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>395734.68</v>
+        <v>390492.2</v>
       </c>
       <c r="M80" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>370017.16</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>5143.24</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>390478.03</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>364873.92</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>5071.75</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>-19.89</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>390458.14</v>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
